--- a/FHD/resources/templates/发货单模板.xlsx
+++ b/FHD/resources/templates/发货单模板.xlsx
@@ -662,7 +662,6 @@
           <t>大写人民币：</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
